--- a/assets/downloads/CotizacionJHONNY QUISPE OCHOA.xlsx
+++ b/assets/downloads/CotizacionJHONNY QUISPE OCHOA.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId4"/>
@@ -53,7 +53,7 @@
     <t>PESO:</t>
   </si>
   <si>
-    <t>0 Kg</t>
+    <t>526 Kg</t>
   </si>
   <si>
     <t>DNI/RUC:</t>
@@ -113,9 +113,9 @@
     <t>Hola JHONNY QUISPE OCHOA 😁 un gusto saludarte!
         A continuación te envío la cotización final de tu importación📋📦.
         🙋‍♂️ PAGO PENDIENTE :
-        ☑️Costo CBM: $0
-        ☑️Impuestos: $383.51
-        ☑️ Total: $383.51
+        ☑️Costo CBM: $415.8
+        ☑️Impuestos: $679.97
+        ☑️ Total: $1095.77
         Pronto le aviso nuevos avances, que tengan buen día🚢
         Último día de pago:</t>
   </si>
@@ -174,19 +174,19 @@
     <t>PRECIO UNIT. (SOLES)</t>
   </si>
   <si>
-    <t>FOCOS LED 12W</t>
-  </si>
-  <si>
-    <t>REBANADOR MULTIFUNCIONAL PARA PLATANOS</t>
-  </si>
-  <si>
-    <t>ROLLO DE ETIQUETA ADHESIVA COLOR</t>
-  </si>
-  <si>
-    <t>ROLLO DE ETIQUETA ADHESIVA BLANCA</t>
-  </si>
-  <si>
-    <t>ETIQUETA ADHESIVA TERMINCAS BLANCA</t>
+    <t>ROLLO DE ETIQUETA DE 10*12 CM</t>
+  </si>
+  <si>
+    <t>ROLLO DE ETIQUETA DE 7.5*2.5 CM</t>
+  </si>
+  <si>
+    <t>ROLLO DE ETIQUETA DE 5.5*4 CM</t>
+  </si>
+  <si>
+    <t>ETIQUETAS DE EMBALAJE</t>
+  </si>
+  <si>
+    <t>MAQUINA CORTADORA DE VEGETALES</t>
   </si>
   <si>
     <t>NOTAS:</t>
@@ -1724,7 +1724,9 @@
       <c r="B10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="16"/>
+      <c r="C10" s="16">
+        <v>40103705</v>
+      </c>
       <c r="D10" s="36"/>
       <c r="E10" s="27" t="s">
         <v>13</v>
@@ -1745,7 +1747,9 @@
       <c r="B11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="17"/>
+      <c r="C11" s="17">
+        <v>51956306757</v>
+      </c>
       <c r="D11" s="37"/>
       <c r="E11" s="24" t="s">
         <v>17</v>
@@ -2110,7 +2114,7 @@
       <c r="I30" s="51"/>
       <c r="J30" s="51"/>
       <c r="K30" s="14" t="str">
-        <f>IF('2'!L7&lt;1, '2'!L7*J11, '2'!L7*J11)</f>
+        <f>IF(J11&lt;1, '2'!L7, '2'!L7*J11)</f>
         <v>0</v>
       </c>
       <c r="L30" s="9" t="s">
@@ -3221,11 +3225,11 @@
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="2" max="2" width="24.708252" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="16.424561" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="45.845947" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="38.847656" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="39.990234" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="41.132813" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="35.2771" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="37.705078" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="35.2771" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="25.85083" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="36.419678" bestFit="true" customWidth="true" style="0"/>
     <col min="8" max="8" width="12.854004" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
@@ -3282,7 +3286,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="84">
-        <v>0</v>
+        <v>526</v>
       </c>
       <c r="K6" s="78" t="s">
         <v>94</v>
@@ -3310,30 +3314,34 @@
       <c r="G7" s="76">
         <v>0</v>
       </c>
-      <c r="H7" s="85"/>
+      <c r="H7" s="85">
+        <v>1.23</v>
+      </c>
       <c r="K7" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="79"/>
+      <c r="L7" s="79">
+        <v>350</v>
+      </c>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="76" t="s">
         <v>97</v>
       </c>
       <c r="C8" s="83">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="D8" s="83">
-        <v>110</v>
+        <v>1.07</v>
       </c>
       <c r="E8" s="83">
-        <v>3.2</v>
+        <v>0.34553191489362</v>
       </c>
       <c r="F8" s="83">
-        <v>2.125</v>
+        <v>3.25</v>
       </c>
       <c r="G8" s="83">
-        <v>3.4</v>
+        <v>270</v>
       </c>
       <c r="H8" s="76"/>
     </row>
@@ -3363,19 +3371,19 @@
         <v>99</v>
       </c>
       <c r="C10" s="76">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="D10" s="76">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="E10" s="76">
-        <v>60</v>
+        <v>940</v>
       </c>
       <c r="F10" s="76">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G10" s="76">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="H10" s="76" t="str">
         <f>SUM(C10:G10)</f>
@@ -3471,27 +3479,27 @@
         <v>103</v>
       </c>
       <c r="C14" s="83" t="str">
-        <f>ROUNDUP(H14*C13,2)</f>
+        <f>H14*C13</f>
         <v>0</v>
       </c>
       <c r="D14" s="83" t="str">
-        <f>ROUNDUP(H14*D13,2)</f>
+        <f>H14*D13</f>
         <v>0</v>
       </c>
       <c r="E14" s="83" t="str">
-        <f>ROUNDUP(H14*E13,2)</f>
+        <f>H14*E13</f>
         <v>0</v>
       </c>
       <c r="F14" s="83" t="str">
-        <f>ROUNDUP(H14*F13,2)</f>
+        <f>H14*F13</f>
         <v>0</v>
       </c>
       <c r="G14" s="83" t="str">
-        <f>ROUNDUP(H14*G13,2)</f>
+        <f>H14*G13</f>
         <v>0</v>
       </c>
       <c r="H14" s="88" t="str">
-        <f>IF(H7&lt;1, ROUNDUP(L7*0.6, 0), ROUNDUP(L7*0.6*H7, 0))</f>
+        <f>IF(H7&lt;1, L7*0.6, L7*0.6*H7)</f>
         <v>0</v>
       </c>
     </row>
@@ -3500,23 +3508,23 @@
         <v>104</v>
       </c>
       <c r="C15" s="83" t="str">
-        <f>ROUNDUP(C11+C14,2)</f>
+        <f>C11+C14</f>
         <v>0</v>
       </c>
       <c r="D15" s="83" t="str">
-        <f>ROUNDUP(D11+D14,2)</f>
+        <f>D11+D14</f>
         <v>0</v>
       </c>
       <c r="E15" s="83" t="str">
-        <f>ROUNDUP(E11+E14,2)</f>
+        <f>E11+E14</f>
         <v>0</v>
       </c>
       <c r="F15" s="83" t="str">
-        <f>ROUNDUP(F11+F14,2)</f>
+        <f>F11+F14</f>
         <v>0</v>
       </c>
       <c r="G15" s="83" t="str">
-        <f>ROUNDUP(G11+G14,2)</f>
+        <f>G11+G14</f>
         <v>0</v>
       </c>
       <c r="H15" s="88" t="str">
@@ -3529,23 +3537,23 @@
         <v>105</v>
       </c>
       <c r="C16" s="83" t="str">
-        <f>ROUNDUP(C12+C14,2)</f>
+        <f>C12+C14</f>
         <v>0</v>
       </c>
       <c r="D16" s="83" t="str">
-        <f>ROUNDUP(D12+D14,2)</f>
+        <f>D12+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="83" t="str">
-        <f>ROUNDUP(E12+E14,2)</f>
+        <f>E12+E14</f>
         <v>0</v>
       </c>
       <c r="F16" s="83" t="str">
-        <f>ROUNDUP(F12+F14,2)</f>
+        <f>F12+F14</f>
         <v>0</v>
       </c>
       <c r="G16" s="83" t="str">
-        <f>ROUNDUP(G12+G14,2)</f>
+        <f>G12+G14</f>
         <v>0</v>
       </c>
       <c r="H16" s="88" t="str">
@@ -3558,23 +3566,23 @@
         <v>106</v>
       </c>
       <c r="C17" s="83" t="str">
-        <f>IF(H15&gt;5000,ROUND(100*C13,2),ROUND(50*C13,2))</f>
+        <f>IF(H15&gt;5000,100*C13,50*C13)</f>
         <v>0</v>
       </c>
       <c r="D17" s="83" t="str">
-        <f>IF(H15&gt;5000,ROUND(100*D13,2),ROUND(50*D13,2))</f>
+        <f>IF(H15&gt;5000,100*D13,50*D13)</f>
         <v>0</v>
       </c>
       <c r="E17" s="83" t="str">
-        <f>IF(H15&gt;5000,ROUND(100*E13,2),ROUND(50*E13,2))</f>
+        <f>IF(H15&gt;5000,100*E13,50*E13)</f>
         <v>0</v>
       </c>
       <c r="F17" s="83" t="str">
-        <f>IF(H15&gt;5000,ROUND(100*F13,2),ROUND(50*F13,2))</f>
+        <f>IF(H15&gt;5000,100*F13,50*F13)</f>
         <v>0</v>
       </c>
       <c r="G17" s="83" t="str">
-        <f>IF(H15&gt;5000,ROUND(100*G13,2),ROUND(50*G13,2))</f>
+        <f>IF(H15&gt;5000,100*G13,50*G13)</f>
         <v>0</v>
       </c>
       <c r="H17" s="88" t="str">
@@ -3587,23 +3595,23 @@
         <v>107</v>
       </c>
       <c r="C18" s="83" t="str">
-        <f>ROUNDUP(C15+C17,2)</f>
+        <f>C15+C17</f>
         <v>0</v>
       </c>
       <c r="D18" s="83" t="str">
-        <f>ROUNDUP(D15+D17,2)</f>
+        <f>D15+D17</f>
         <v>0</v>
       </c>
       <c r="E18" s="83" t="str">
-        <f>ROUNDUP(E15+E17,2)</f>
+        <f>E15+E17</f>
         <v>0</v>
       </c>
       <c r="F18" s="83" t="str">
-        <f>ROUNDUP(F15+F17,2)</f>
+        <f>F15+F17</f>
         <v>0</v>
       </c>
       <c r="G18" s="83" t="str">
-        <f>ROUNDUP(G15+G17,2)</f>
+        <f>G15+G17</f>
         <v>0</v>
       </c>
       <c r="H18" s="88" t="str">
@@ -3616,23 +3624,23 @@
         <v>108</v>
       </c>
       <c r="C19" s="83" t="str">
-        <f>ROUNDUP(C16+C17,2)</f>
+        <f>C16+C17</f>
         <v>0</v>
       </c>
       <c r="D19" s="83" t="str">
-        <f>ROUNDUP(D16+D17,2)</f>
+        <f>D16+D17</f>
         <v>0</v>
       </c>
       <c r="E19" s="83" t="str">
-        <f>ROUNDUP(E16+E17,2)</f>
+        <f>E16+E17</f>
         <v>0</v>
       </c>
       <c r="F19" s="83" t="str">
-        <f>ROUNDUP(F16+F17,2)</f>
+        <f>F16+F17</f>
         <v>0</v>
       </c>
       <c r="G19" s="83" t="str">
-        <f>ROUNDUP(G16+G17,2)</f>
+        <f>G16+G17</f>
         <v>0</v>
       </c>
       <c r="H19" s="88" t="str">
@@ -3677,13 +3685,13 @@
         <v>0</v>
       </c>
       <c r="D27" s="89">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="E27" s="89">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F27" s="89">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G27" s="89">
         <v>0</v>
@@ -3871,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="83" t="str">
-        <f>IF(H7&lt;1, ROUNDUP(L7*0.4, 0), ROUNDUP(L7*0.4*H7, 0))</f>
+        <f>IF(H7&lt;1, L7*0.4,L7*0.4*H7)</f>
         <v>0</v>
       </c>
     </row>
@@ -3906,23 +3914,23 @@
         <v>115</v>
       </c>
       <c r="C44" s="83" t="str">
-        <f>SUM(C15,C40,C32,(C26*C10))</f>
+        <f>SUM(C15,C40,C32,(C26))</f>
         <v>0</v>
       </c>
       <c r="D44" s="83" t="str">
-        <f>SUM(D15,D40,D32,(D26*D10))</f>
+        <f>SUM(D15,D40,D32,(D26))</f>
         <v>0</v>
       </c>
       <c r="E44" s="83" t="str">
-        <f>SUM(E15,E40,E32,(E26*E10))</f>
+        <f>SUM(E15,E40,E32,(E26))</f>
         <v>0</v>
       </c>
       <c r="F44" s="83" t="str">
-        <f>SUM(F15,F40,F32,(F26*F10))</f>
+        <f>SUM(F15,F40,F32,(F26))</f>
         <v>0</v>
       </c>
       <c r="G44" s="83" t="str">
-        <f>SUM(G15,G40,G32,(G26*G10))</f>
+        <f>SUM(G15,G40,G32,(G26))</f>
         <v>0</v>
       </c>
       <c r="H44" s="83" t="str">
@@ -3935,19 +3943,19 @@
         <v>45</v>
       </c>
       <c r="C45" s="76">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="D45" s="76">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="E45" s="76">
-        <v>60</v>
+        <v>940</v>
       </c>
       <c r="F45" s="76">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G45" s="76">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="H45" s="76"/>
     </row>
@@ -3956,23 +3964,23 @@
         <v>116</v>
       </c>
       <c r="C46" s="83" t="str">
-        <f>ROUND(SUM(C44/C45),2)</f>
+        <f>SUM(C44/C45)</f>
         <v>0</v>
       </c>
       <c r="D46" s="83" t="str">
-        <f>ROUND(SUM(D44/D45),2)</f>
+        <f>SUM(D44/D45)</f>
         <v>0</v>
       </c>
       <c r="E46" s="83" t="str">
-        <f>ROUND(SUM(E44/E45),2)</f>
+        <f>SUM(E44/E45)</f>
         <v>0</v>
       </c>
       <c r="F46" s="83" t="str">
-        <f>ROUND(SUM(F44/F45),2)</f>
+        <f>SUM(F44/F45)</f>
         <v>0</v>
       </c>
       <c r="G46" s="83" t="str">
-        <f>ROUND(SUM(G44/G45),2)</f>
+        <f>SUM(G44/G45)</f>
         <v>0</v>
       </c>
       <c r="H46" s="76"/>
@@ -3982,23 +3990,23 @@
         <v>117</v>
       </c>
       <c r="C47" s="87" t="str">
-        <f>ROUND(C46*3.7,2)</f>
+        <f>C46*3.7</f>
         <v>0</v>
       </c>
       <c r="D47" s="87" t="str">
-        <f>ROUND(D46*3.7,2)</f>
+        <f>D46*3.7</f>
         <v>0</v>
       </c>
       <c r="E47" s="87" t="str">
-        <f>ROUND(E46*3.7,2)</f>
+        <f>E46*3.7</f>
         <v>0</v>
       </c>
       <c r="F47" s="87" t="str">
-        <f>ROUND(F46*3.7,2)</f>
+        <f>F46*3.7</f>
         <v>0</v>
       </c>
       <c r="G47" s="87" t="str">
-        <f>ROUND(G46*3.7,2)</f>
+        <f>G46*3.7</f>
         <v>0</v>
       </c>
       <c r="H47" s="76"/>
